--- a/data/trans_dic/IP16B01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,11; 94,67</t>
+          <t>53,25; 94,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,22; 100,0</t>
+          <t>67,4; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,72; 93,42</t>
+          <t>48,93; 93,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70,92; 94,82</t>
+          <t>68,66; 94,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>71,09; 96,32</t>
+          <t>68,45; 96,32</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,12</t>
+          <t>0,0; 21,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,46; 92,45</t>
+          <t>59,65; 92,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,14; 92,79</t>
+          <t>39,26; 92,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,31; 100,0</t>
+          <t>71,84; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,32</t>
+          <t>0,0; 10,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,8; 94,79</t>
+          <t>72,22; 94,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,29; 96,72</t>
+          <t>70,25; 96,68</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,51; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,49; 100,0</t>
+          <t>39,24; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69,42; 100,0</t>
+          <t>68,04; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,51; 100,0</t>
+          <t>37,64; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,1; 100,0</t>
+          <t>76,76; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,21; 94,29</t>
+          <t>50,83; 93,97</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,86; 87,62</t>
+          <t>60,7; 87,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,79; 93,72</t>
+          <t>69,78; 93,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,36; 100,0</t>
+          <t>86,76; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,76; 95,55</t>
+          <t>58,53; 95,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,97; 93,0</t>
+          <t>79,0; 92,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,05; 91,13</t>
+          <t>72,82; 91,48</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,34; 96,23</t>
+          <t>65,16; 96,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,02; 90,61</t>
+          <t>54,07; 90,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,55; 100,0</t>
+          <t>75,73; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,0; 100,0</t>
+          <t>68,18; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,69; 94,69</t>
+          <t>77,38; 95,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,94; 92,23</t>
+          <t>67,55; 92,67</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,76; 100,0</t>
+          <t>43,51; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,12; 92,17</t>
+          <t>35,53; 91,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,95; 100,0</t>
+          <t>66,54; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68,93; 100,0</t>
+          <t>69,83; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54,82; 94,39</t>
+          <t>53,5; 94,41</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 4,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,13; 88,12</t>
+          <t>74,77; 88,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71,94; 87,82</t>
+          <t>72,53; 88,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,48; 96,97</t>
+          <t>87,85; 96,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,21; 93,32</t>
+          <t>79,38; 93,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,58; 91,87</t>
+          <t>84,13; 91,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,08; 88,48</t>
+          <t>78,14; 88,74</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7288</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13534</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7344</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14632</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7234; 12859</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10194; 15124</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4580; 8739</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>19712; 26997</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>11395; 16036</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13858</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5279</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7341</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11799</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>21199</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>17078</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4152</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10282; 15920</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2802; 6604</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8940; 12443</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4071</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17750; 23332</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13756; 18930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8884</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4165</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>17819</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9137</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2535; 6460</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6548; 9624</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1836; 4878</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14246; 18559</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5764; 10654</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20871</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22807</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31820</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>52690</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>35110</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16614; 23937</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18760; 25240</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>28822; 33220</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8789; 14314</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>47866; 56173</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>30509; 38330</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16444</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11803</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17569</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15345</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>34014</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>27148</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12588; 18584</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8376; 14082</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14434; 19059</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11631; 17061</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>29698; 36743</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>21989; 30166</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4283</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7502</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11784</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10099</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2153; 4948</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3219; 8328</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>5421; 8147</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>9144; 13095</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>6937; 12242</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>75439</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>58341</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>86650</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>54863</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>162089</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>113204</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4725</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>68341; 80694</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>52453; 63785</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>81273; 89553</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>49743; 58533</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4729</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>154721; 168933</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>105470; 119783</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Clase-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,25; 94,65</t>
+          <t>54,62; 94,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,4; 100,0</t>
+          <t>63,8; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,93; 93,36</t>
+          <t>48,84; 93,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,66; 94,03</t>
+          <t>71,11; 94,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,45; 96,32</t>
+          <t>71,0; 100,0</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 21,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,65; 92,36</t>
+          <t>60,65; 92,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,26; 92,53</t>
+          <t>43,0; 92,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 100,0</t>
+          <t>73,1; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,92</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,22; 94,93</t>
+          <t>72,63; 94,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,25; 96,68</t>
+          <t>70,37; 96,65</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,24; 100,0</t>
+          <t>42,42; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,04; 100,0</t>
+          <t>67,09; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,64; 100,0</t>
+          <t>40,34; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76,76; 100,0</t>
+          <t>79,66; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,83; 93,97</t>
+          <t>53,44; 93,97</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,7; 87,45</t>
+          <t>61,26; 87,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,78; 93,89</t>
+          <t>70,24; 93,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,76; 100,0</t>
+          <t>85,86; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,53; 95,32</t>
+          <t>60,24; 95,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79,0; 92,71</t>
+          <t>78,73; 93,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,82; 91,48</t>
+          <t>72,07; 91,65</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,16; 96,19</t>
+          <t>67,22; 96,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,07; 90,91</t>
+          <t>55,15; 90,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,73; 100,0</t>
+          <t>75,52; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,18; 100,0</t>
+          <t>69,39; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,38; 95,73</t>
+          <t>77,32; 95,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,55; 92,67</t>
+          <t>71,05; 93,32</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,51; 100,0</t>
+          <t>41,63; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,53; 91,92</t>
+          <t>35,54; 91,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,54; 100,0</t>
+          <t>60,11; 100,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,83; 100,0</t>
+          <t>70,02; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,5; 94,41</t>
+          <t>56,1; 94,46</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,31</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,77; 88,29</t>
+          <t>75,22; 88,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,53; 88,2</t>
+          <t>72,01; 86,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,85; 96,8</t>
+          <t>87,94; 97,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,38; 93,4</t>
+          <t>79,11; 92,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,13; 91,85</t>
+          <t>84,12; 91,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,14; 88,74</t>
+          <t>78,38; 88,74</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7234; 12859</t>
+          <t>7420; 12850</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10194; 15124</t>
+          <t>9648; 15124</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4580; 8739</t>
+          <t>4571; 8736</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19712; 26997</t>
+          <t>20417; 27132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11395; 16036</t>
+          <t>11820; 16648</t>
         </is>
       </c>
     </row>
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4152</t>
+          <t>0; 4175</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10282; 15920</t>
+          <t>10454; 15931</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2802; 6604</t>
+          <t>3069; 6597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8940; 12443</t>
+          <t>9096; 12443</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4071</t>
+          <t>0; 4128</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17750; 23332</t>
+          <t>17851; 23318</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13756; 18930</t>
+          <t>13778; 18923</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2535; 6460</t>
+          <t>2740; 6460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1985,12 +1985,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6548; 9624</t>
+          <t>6456; 9624</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1836; 4878</t>
+          <t>1968; 4878</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14246; 18559</t>
+          <t>14785; 18559</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5764; 10654</t>
+          <t>6060; 10654</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16614; 23937</t>
+          <t>16767; 23965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18760; 25240</t>
+          <t>18883; 25212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28822; 33220</t>
+          <t>28521; 33220</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8789; 14314</t>
+          <t>9047; 14347</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47866; 56173</t>
+          <t>47701; 56690</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30509; 38330</t>
+          <t>30195; 38402</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12588; 18584</t>
+          <t>12986; 18621</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8376; 14082</t>
+          <t>8543; 14066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14434; 19059</t>
+          <t>14393; 19059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11631; 17061</t>
+          <t>11839; 17061</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29698; 36743</t>
+          <t>29675; 36763</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21989; 30166</t>
+          <t>23129; 30375</t>
         </is>
       </c>
     </row>
@@ -2459,12 +2459,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2153; 4948</t>
+          <t>2060; 4948</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3219; 8328</t>
+          <t>3220; 8284</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5421; 8147</t>
+          <t>4897; 8147</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9144; 13095</t>
+          <t>9169; 13095</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6937; 12242</t>
+          <t>7274; 12249</t>
         </is>
       </c>
     </row>
@@ -2617,17 +2617,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4725</t>
+          <t>0; 5040</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68341; 80694</t>
+          <t>68750; 80821</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52453; 63785</t>
+          <t>52073; 62890</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2637,27 +2637,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>81273; 89553</t>
+          <t>81356; 89830</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49743; 58533</t>
+          <t>49574; 58101</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4729</t>
+          <t>0; 5403</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>154721; 168933</t>
+          <t>154701; 168992</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>105470; 119783</t>
+          <t>105799; 119778</t>
         </is>
       </c>
     </row>
